--- a/file/Circular_Cloud_System_Web_VPATJ03740.xlsx
+++ b/file/Circular_Cloud_System_Web_VPATJ03740.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3ACF704-C9DC-4CA5-A3BC-F6AD6B19CA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C54B19F-3F6A-47D8-BD1C-020121948AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BDA978F9-126E-4B01-AE3A-1356FA8E3D07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{72C7A87E-BDC2-45CD-9CEF-57F4BCBD2000}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="232">
   <si>
     <r>
       <t>ICT</t>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>18</t>
+      <t>24</t>
     </r>
     <r>
       <rPr>
@@ -428,7 +428,42 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
+      <t>評価不要</t>
+    </r>
+    <rPh sb="0" eb="4">
+      <t>ヒョウカフヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>米国リハビリテーション法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>508</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>条を用いているため評価の対象外である。</t>
     </r>
     <phoneticPr fontId="3"/>
   </si>
@@ -507,6 +542,19 @@
         <charset val="128"/>
       </rPr>
       <t>発話能力なしでの使用</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="3"/>
   </si>
@@ -2514,7 +2562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0E0349-CAD2-48C4-9DB9-176DE32F356F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E27A29-19E8-40FC-AF60-17BB07C921BA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2814,7 +2862,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>24</v>
       </c>
@@ -2823,30 +2871,30 @@
       <c r="D22" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38"/>
+      <c r="E22" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
@@ -2863,7 +2911,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2876,7 +2924,7 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
@@ -2893,7 +2941,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -2906,12 +2954,12 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>20</v>
@@ -2923,7 +2971,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -2936,7 +2984,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -2953,7 +3001,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -2966,7 +3014,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -2979,7 +3027,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -2992,15 +3040,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3009,7 +3057,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3050,15 +3098,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3067,7 +3115,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3091,7 +3139,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3121,15 +3169,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3138,7 +3186,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3162,10 +3210,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3188,7 +3236,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3333,7 +3381,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E48E7C-87C3-4EA8-ADFD-BB8754A22EB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15AEE3F-D56A-433D-BCE5-9247BCAF7ACC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3346,43 +3394,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3390,36 +3438,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3427,10 +3475,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3448,14 +3496,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3471,15 +3519,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3494,15 +3542,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3517,17 +3565,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3540,10 +3588,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3551,7 +3599,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3563,10 +3611,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3575,7 +3623,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3586,10 +3634,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3599,10 +3647,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3611,10 +3659,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3624,10 +3672,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3636,10 +3684,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3657,17 +3705,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3682,10 +3730,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3703,10 +3751,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3721,17 +3769,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3744,17 +3792,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3767,20 +3815,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3792,20 +3840,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3817,17 +3865,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3843,10 +3891,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3854,7 +3902,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3863,23 +3911,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3888,23 +3936,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3916,15 +3964,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -3939,15 +3987,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -3962,27 +4010,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -3991,10 +4039,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4012,29 +4060,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4043,10 +4091,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4064,17 +4112,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4089,10 +4137,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4110,30 +4158,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4141,10 +4189,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4162,31 +4210,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4195,10 +4243,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4216,15 +4264,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4239,14 +4287,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4262,10 +4310,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4275,10 +4323,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4287,27 +4335,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4316,10 +4364,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4329,10 +4377,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4341,14 +4389,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4364,10 +4412,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4377,10 +4425,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4389,10 +4437,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4402,10 +4450,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4414,10 +4462,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4435,10 +4483,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4456,10 +4504,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4477,14 +4525,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4500,10 +4548,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4521,15 +4569,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4544,10 +4592,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4565,20 +4613,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4590,10 +4638,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4611,29 +4659,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4642,10 +4690,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4663,10 +4711,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4674,7 +4722,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4686,10 +4734,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4697,7 +4745,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4709,10 +4757,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4720,7 +4768,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4732,10 +4780,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4753,24 +4801,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4782,17 +4830,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4805,20 +4853,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4830,10 +4878,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4851,14 +4899,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4874,10 +4922,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4895,22 +4943,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4922,10 +4970,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -4943,31 +4991,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -4976,10 +5024,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -4997,29 +5045,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5028,14 +5076,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5043,10 +5091,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5055,43 +5103,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5101,22 +5149,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5126,22 +5174,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5151,32 +5199,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5185,23 +5233,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5210,26 +5258,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5237,23 +5285,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5265,31 +5313,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5298,10 +5346,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5319,15 +5367,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5342,14 +5390,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5357,10 +5405,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5369,22 +5417,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5396,24 +5444,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5425,10 +5473,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5446,24 +5494,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5472,25 +5520,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5499,20 +5547,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5527,24 +5575,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5556,24 +5604,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
